--- a/Randomization/Outputs/randomization_final.xlsx
+++ b/Randomization/Outputs/randomization_final.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="771">
   <si>
     <t>id_infra</t>
   </si>
@@ -132,48 +132,48 @@
     <t>GOLO-DJIGBE</t>
   </si>
   <si>
+    <t>GODOMEY</t>
+  </si>
+  <si>
+    <t>HEVIE</t>
+  </si>
+  <si>
+    <t>ABOMEY-CALAVI</t>
+  </si>
+  <si>
+    <t>OUEDO</t>
+  </si>
+  <si>
+    <t>ZINVIE</t>
+  </si>
+  <si>
     <t>TOGBA</t>
   </si>
   <si>
-    <t>ABOMEY-CALAVI</t>
+    <t>GOLO-DJIGBE</t>
+  </si>
+  <si>
+    <t>AKASSATO</t>
+  </si>
+  <si>
+    <t>GODOMEY</t>
   </si>
   <si>
     <t>OUEDO</t>
   </si>
   <si>
-    <t>ZINVIE</t>
+    <t>AKASSATO</t>
   </si>
   <si>
     <t>GODOMEY</t>
   </si>
   <si>
-    <t>HEVIE</t>
-  </si>
-  <si>
-    <t>TOGBA</t>
-  </si>
-  <si>
-    <t>GOLO-DJIGBE</t>
-  </si>
-  <si>
     <t>AKASSATO</t>
   </si>
   <si>
-    <t>GODOMEY</t>
-  </si>
-  <si>
-    <t>OUEDO</t>
-  </si>
-  <si>
-    <t>AKASSATO</t>
-  </si>
-  <si>
     <t>KPANROUN</t>
   </si>
   <si>
-    <t>GODOMEY</t>
-  </si>
-  <si>
     <t>ADANHONDJIGO</t>
   </si>
   <si>
@@ -216,27 +216,27 @@
     <t>AGBANOU</t>
   </si>
   <si>
+    <t>SEKOU</t>
+  </si>
+  <si>
+    <t>LISSEGAZOUN</t>
+  </si>
+  <si>
+    <t>LON-AGONMEY</t>
+  </si>
+  <si>
+    <t>ALLADA CENTRE</t>
+  </si>
+  <si>
+    <t>AVAKPA</t>
+  </si>
+  <si>
     <t>ATTOGON</t>
   </si>
   <si>
-    <t>SEKOU</t>
-  </si>
-  <si>
-    <t>LISSEGAZOUN</t>
-  </si>
-  <si>
-    <t>LON-AGONMEY</t>
-  </si>
-  <si>
     <t>TOGOUDO</t>
   </si>
   <si>
-    <t>ALLADA CENTRE</t>
-  </si>
-  <si>
-    <t>AVAKPA</t>
-  </si>
-  <si>
     <t>LISSEZOUN</t>
   </si>
   <si>
@@ -570,27 +570,27 @@
     <t>CEG 1 GOLO-DJIGBE</t>
   </si>
   <si>
+    <t>CEG DU PLATEAU</t>
+  </si>
+  <si>
+    <t>CEG HEVIE</t>
+  </si>
+  <si>
+    <t>CEG KANSOUNKPA</t>
+  </si>
+  <si>
+    <t>CEG LA VERDURE</t>
+  </si>
+  <si>
+    <t>CEG ZINVIE</t>
+  </si>
+  <si>
     <t>CEG AHOSSOU GBETA</t>
   </si>
   <si>
     <t>CEG HOUETO</t>
   </si>
   <si>
-    <t>CEG KANSOUNKPA</t>
-  </si>
-  <si>
-    <t>CEG LA VERDURE</t>
-  </si>
-  <si>
-    <t>CEG ZINVIE</t>
-  </si>
-  <si>
-    <t>CEG DU PLATEAU</t>
-  </si>
-  <si>
-    <t>CEG HEVIE</t>
-  </si>
-  <si>
     <t>CEG TANKPE</t>
   </si>
   <si>
@@ -600,30 +600,30 @@
     <t>CEG 3 GOLO DJIGBE</t>
   </si>
   <si>
+    <t>CEG ADJAGBO</t>
+  </si>
+  <si>
     <t>CEG AGASSA-GODOMEY</t>
   </si>
   <si>
+    <t>CEG LOBOZOUNKPA</t>
+  </si>
+  <si>
+    <t>CEG OUEDO KPOSSIDJA</t>
+  </si>
+  <si>
     <t>CEG AKASSATO</t>
   </si>
   <si>
     <t>CEG ATROKPOCODJI</t>
   </si>
   <si>
-    <t>CEG OUEDO KPOSSIDJA</t>
-  </si>
-  <si>
-    <t>CEG ADJAGBO</t>
-  </si>
-  <si>
     <t>CEG GBETAGBO</t>
   </si>
   <si>
     <t>CEG KPANROUN</t>
   </si>
   <si>
-    <t>CEG LOBOZOUNKPA</t>
-  </si>
-  <si>
     <t>CEG ADANHONDJIGON</t>
   </si>
   <si>
@@ -669,27 +669,27 @@
     <t>CEG AGBANOU</t>
   </si>
   <si>
+    <t>CEG DODJI DEHE</t>
+  </si>
+  <si>
+    <t>CEG LISSEGAZOUN</t>
+  </si>
+  <si>
+    <t>CEG LON AGONMEY</t>
+  </si>
+  <si>
+    <t>CEG SOYO</t>
+  </si>
+  <si>
+    <t>CEG UNION AVA</t>
+  </si>
+  <si>
     <t>CEG ATTOGON</t>
   </si>
   <si>
-    <t>CEG DODJI DEHE</t>
-  </si>
-  <si>
-    <t>CEG LISSEGAZOUN</t>
-  </si>
-  <si>
-    <t>CEG LON AGONMEY</t>
-  </si>
-  <si>
     <t>CEG TOGOUDO ALLADDA</t>
   </si>
   <si>
-    <t>CEG SOYO</t>
-  </si>
-  <si>
-    <t>CEG UNION AVA</t>
-  </si>
-  <si>
     <t>CEG 2 BOHICON</t>
   </si>
   <si>
@@ -1224,15 +1224,15 @@
     <t>RURAL</t>
   </si>
   <si>
-    <t>PERIURBAN</t>
+    <t>MILIEU_ADMIN</t>
+  </si>
+  <si>
+    <t>URBAIN</t>
   </si>
   <si>
     <t>RURAL</t>
   </si>
   <si>
-    <t>MILIEU_ADMIN</t>
-  </si>
-  <si>
     <t>URBAIN</t>
   </si>
   <si>
@@ -1569,9 +1569,18 @@
     <t>assigned_group</t>
   </si>
   <si>
+    <t>Salience + Implementation</t>
+  </si>
+  <si>
     <t>Salience</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Salience</t>
+  </si>
+  <si>
     <t>Salience + Implementation</t>
   </si>
   <si>
@@ -1587,9 +1596,15 @@
     <t>Control</t>
   </si>
   <si>
+    <t>Salience</t>
+  </si>
+  <si>
     <t>Salience + Implementation</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
     <t>Salience</t>
   </si>
   <si>
@@ -1599,9 +1614,27 @@
     <t>Salience + Implementation</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Salience + Implementation</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
     <t>Salience</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Salience</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
     <t>Salience + Implementation</t>
   </si>
   <si>
@@ -1611,6 +1644,9 @@
     <t>Control</t>
   </si>
   <si>
+    <t>Salience + Implementation</t>
+  </si>
+  <si>
     <t>Salience</t>
   </si>
   <si>
@@ -1620,48 +1656,93 @@
     <t>Salience + Implementation</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
     <t>Salience</t>
   </si>
   <si>
+    <t>Salience + Implementation</t>
+  </si>
+  <si>
+    <t>Salience</t>
+  </si>
+  <si>
     <t>Control</t>
   </si>
   <si>
     <t>Salience</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Salience</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Salience</t>
+  </si>
+  <si>
     <t>Salience + Implementation</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
     <t>Salience</t>
   </si>
   <si>
     <t>Control</t>
   </si>
   <si>
+    <t>Salience + Implementation</t>
+  </si>
+  <si>
     <t>Salience</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Salience</t>
+  </si>
+  <si>
     <t>Salience + Implementation</t>
   </si>
   <si>
     <t>Control</t>
   </si>
   <si>
+    <t>Salience</t>
+  </si>
+  <si>
     <t>Salience + Implementation</t>
   </si>
   <si>
     <t>Salience</t>
   </si>
   <si>
+    <t>Salience + Implementation</t>
+  </si>
+  <si>
     <t>Control</t>
   </si>
   <si>
     <t>Salience</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
     <t>Salience + Implementation</t>
   </si>
   <si>
+    <t>Salience</t>
+  </si>
+  <si>
     <t>Control</t>
   </si>
   <si>
@@ -1671,36 +1752,75 @@
     <t>Control</t>
   </si>
   <si>
+    <t>Salience + Implementation</t>
+  </si>
+  <si>
     <t>Salience</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
     <t>Salience + Implementation</t>
   </si>
   <si>
     <t>Control</t>
   </si>
   <si>
+    <t>Salience</t>
+  </si>
+  <si>
     <t>Salience + Implementation</t>
   </si>
   <si>
     <t>Control</t>
   </si>
   <si>
+    <t>Salience + Implementation</t>
+  </si>
+  <si>
     <t>Salience</t>
   </si>
   <si>
     <t>Salience + Implementation</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Salience + Implementation</t>
+  </si>
+  <si>
     <t>Salience</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Salience</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Salience</t>
+  </si>
+  <si>
     <t>Salience + Implementation</t>
   </si>
   <si>
+    <t>Salience</t>
+  </si>
+  <si>
     <t>Control</t>
   </si>
   <si>
+    <t>Salience + Implementation</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
     <t>Salience</t>
   </si>
   <si>
@@ -1710,9 +1830,21 @@
     <t>Salience + Implementation</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Salience + Implementation</t>
+  </si>
+  <si>
     <t>Salience</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Salience</t>
+  </si>
+  <si>
     <t>Salience + Implementation</t>
   </si>
   <si>
@@ -1722,12 +1854,27 @@
     <t>Control</t>
   </si>
   <si>
+    <t>Salience</t>
+  </si>
+  <si>
     <t>Salience + Implementation</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Salience + Implementation</t>
+  </si>
+  <si>
     <t>Salience</t>
   </si>
   <si>
+    <t>Salience + Implementation</t>
+  </si>
+  <si>
+    <t>Salience</t>
+  </si>
+  <si>
     <t>Control</t>
   </si>
   <si>
@@ -1737,6 +1884,15 @@
     <t>Salience</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Salience</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
     <t>Salience + Implementation</t>
   </si>
   <si>
@@ -1755,9 +1911,18 @@
     <t>Salience</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
     <t>Salience + Implementation</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Salience + Implementation</t>
+  </si>
+  <si>
     <t>Salience</t>
   </si>
   <si>
@@ -1770,228 +1935,156 @@
     <t>Salience + Implementation</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
     <t>Salience</t>
   </si>
   <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Salience</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Salience + Implementation</t>
-  </si>
-  <si>
-    <t>Salience</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Salience + Implementation</t>
-  </si>
-  <si>
-    <t>Salience</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Salience</t>
-  </si>
-  <si>
-    <t>Salience + Implementation</t>
-  </si>
-  <si>
-    <t>Salience</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Salience + Implementation</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Salience</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Salience + Implementation</t>
-  </si>
-  <si>
-    <t>Salience</t>
-  </si>
-  <si>
-    <t>Salience + Implementation</t>
-  </si>
-  <si>
-    <t>Salience</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Salience + Implementation</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Salience</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Salience + Implementation</t>
-  </si>
-  <si>
-    <t>Salience</t>
-  </si>
-  <si>
-    <t>Salience + Implementation</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Salience + Implementation</t>
-  </si>
-  <si>
-    <t>Salience</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Salience + Implementation</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Salience + Implementation</t>
-  </si>
-  <si>
-    <t>Salience</t>
-  </si>
-  <si>
-    <t>Salience + Implementation</t>
-  </si>
-  <si>
-    <t>Salience</t>
-  </si>
-  <si>
-    <t>Salience + Implementation</t>
-  </si>
-  <si>
-    <t>Salience</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Salience</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Salience + Implementation</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Salience</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Salience + Implementation</t>
-  </si>
-  <si>
-    <t>Salience</t>
-  </si>
-  <si>
-    <t>Salience + Implementation</t>
-  </si>
-  <si>
-    <t>Salience</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
     <t>targeted_parent</t>
   </si>
   <si>
     <t>Father</t>
   </si>
   <si>
+    <t>Mother</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
+    <t>Mother</t>
+  </si>
+  <si>
     <t>Father</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
+    <t>Father</t>
+  </si>
+  <si>
     <t>Mother</t>
   </si>
   <si>
     <t>Father</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Mother</t>
   </si>
   <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
     <t>Father</t>
   </si>
   <si>
+    <t>Mother</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Mother</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
     <t>Mother</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Father</t>
   </si>
   <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
     <t>Mother</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Father</t>
   </si>
   <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
     <t>Father</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Mother</t>
   </si>
   <si>
@@ -2001,6 +2094,9 @@
     <t>Mother</t>
   </si>
   <si>
+    <t>Father</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -2010,24 +2106,72 @@
     <t>Mother</t>
   </si>
   <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
     <t>Father</t>
   </si>
   <si>
+    <t>Mother</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
     <t>Mother</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Mother</t>
   </si>
   <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -2043,12 +2187,18 @@
     <t>N/A</t>
   </si>
   <si>
+    <t>Father</t>
+  </si>
+  <si>
     <t>Mother</t>
   </si>
   <si>
     <t>Father</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Mother</t>
   </si>
   <si>
@@ -2058,15 +2208,36 @@
     <t>Father</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
     <t>Mother</t>
   </si>
   <si>
+    <t>Father</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
     <t>Father</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Mother</t>
   </si>
   <si>
@@ -2085,6 +2256,12 @@
     <t>Mother</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
     <t>Father</t>
   </si>
   <si>
@@ -2094,172 +2271,55 @@
     <t>Mother</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Father</t>
   </si>
   <si>
+    <t>Mother</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Mother</t>
   </si>
   <si>
     <t>Father</t>
   </si>
   <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
     <t>Mother</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
     <t>Father</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>target_enrol</t>
@@ -2334,7 +2394,7 @@
         <v>334</v>
       </c>
       <c r="G1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="H1" t="s">
         <v>446</v>
@@ -2349,13 +2409,13 @@
         <v>517</v>
       </c>
       <c r="L1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="M1" t="s">
-        <v>749</v>
+        <v>769</v>
       </c>
       <c r="N1" t="s">
-        <v>750</v>
+        <v>770</v>
       </c>
     </row>
     <row r="2">
@@ -2378,7 +2438,7 @@
         <v>335</v>
       </c>
       <c r="G2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H2" t="s">
         <v>447</v>
@@ -2393,7 +2453,7 @@
         <v>518</v>
       </c>
       <c r="L2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="M2" s="1">
         <v>207</v>
@@ -2422,7 +2482,7 @@
         <v>335</v>
       </c>
       <c r="G3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H3" t="s">
         <v>447</v>
@@ -2437,7 +2497,7 @@
         <v>519</v>
       </c>
       <c r="L3" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="M3" s="1">
         <v>461</v>
@@ -2466,7 +2526,7 @@
         <v>335</v>
       </c>
       <c r="G4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H4" t="s">
         <v>447</v>
@@ -2481,7 +2541,7 @@
         <v>520</v>
       </c>
       <c r="L4" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="M4" s="1">
         <v>111</v>
@@ -2510,7 +2570,7 @@
         <v>336</v>
       </c>
       <c r="G5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H5" t="s">
         <v>448</v>
@@ -2522,10 +2582,10 @@
         <v>2</v>
       </c>
       <c r="K5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L5" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="M5" s="1">
         <v>83</v>
@@ -2554,7 +2614,7 @@
         <v>336</v>
       </c>
       <c r="G6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H6" t="s">
         <v>448</v>
@@ -2566,10 +2626,10 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L6" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="M6" s="1">
         <v>57</v>
@@ -2598,7 +2658,7 @@
         <v>336</v>
       </c>
       <c r="G7" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H7" t="s">
         <v>448</v>
@@ -2610,10 +2670,10 @@
         <v>2</v>
       </c>
       <c r="K7" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L7" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="M7" s="1">
         <v>52</v>
@@ -2642,7 +2702,7 @@
         <v>337</v>
       </c>
       <c r="G8" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H8" t="s">
         <v>449</v>
@@ -2657,7 +2717,7 @@
         <v>523</v>
       </c>
       <c r="L8" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="M8" s="1">
         <v>484</v>
@@ -2668,7 +2728,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
@@ -2686,7 +2746,7 @@
         <v>337</v>
       </c>
       <c r="G9" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H9" t="s">
         <v>449</v>
@@ -2698,13 +2758,13 @@
         <v>3</v>
       </c>
       <c r="K9" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L9" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="M9" s="1">
-        <v>602</v>
+        <v>706</v>
       </c>
       <c r="N9" s="1">
         <v>473</v>
@@ -2712,7 +2772,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
@@ -2721,7 +2781,7 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s">
         <v>186</v>
@@ -2730,7 +2790,7 @@
         <v>337</v>
       </c>
       <c r="G10" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H10" t="s">
         <v>449</v>
@@ -2742,13 +2802,13 @@
         <v>3</v>
       </c>
       <c r="K10" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L10" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="M10" s="1">
-        <v>516</v>
+        <v>933</v>
       </c>
       <c r="N10" s="1">
         <v>473</v>
@@ -2765,7 +2825,7 @@
         <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s">
         <v>187</v>
@@ -2774,7 +2834,7 @@
         <v>337</v>
       </c>
       <c r="G11" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H11" t="s">
         <v>449</v>
@@ -2786,10 +2846,10 @@
         <v>3</v>
       </c>
       <c r="K11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L11" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="M11" s="1">
         <v>490</v>
@@ -2809,7 +2869,7 @@
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s">
         <v>188</v>
@@ -2818,7 +2878,7 @@
         <v>337</v>
       </c>
       <c r="G12" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H12" t="s">
         <v>449</v>
@@ -2830,10 +2890,10 @@
         <v>3</v>
       </c>
       <c r="K12" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L12" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="M12" s="1">
         <v>633</v>
@@ -2853,7 +2913,7 @@
         <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
         <v>189</v>
@@ -2862,7 +2922,7 @@
         <v>338</v>
       </c>
       <c r="G13" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H13" t="s">
         <v>449</v>
@@ -2874,10 +2934,10 @@
         <v>3</v>
       </c>
       <c r="K13" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="L13" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="M13" s="1">
         <v>600</v>
@@ -2888,7 +2948,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
@@ -2897,7 +2957,7 @@
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
         <v>190</v>
@@ -2906,7 +2966,7 @@
         <v>339</v>
       </c>
       <c r="G14" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H14" t="s">
         <v>449</v>
@@ -2918,13 +2978,13 @@
         <v>4</v>
       </c>
       <c r="K14" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L14" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="M14" s="1">
-        <v>706</v>
+        <v>602</v>
       </c>
       <c r="N14" s="1">
         <v>473</v>
@@ -2932,7 +2992,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
@@ -2950,7 +3010,7 @@
         <v>339</v>
       </c>
       <c r="G15" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H15" t="s">
         <v>449</v>
@@ -2962,13 +3022,13 @@
         <v>4</v>
       </c>
       <c r="K15" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L15" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="M15" s="1">
-        <v>933</v>
+        <v>516</v>
       </c>
       <c r="N15" s="1">
         <v>473</v>
@@ -2985,7 +3045,7 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s">
         <v>192</v>
@@ -2994,7 +3054,7 @@
         <v>339</v>
       </c>
       <c r="G16" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H16" t="s">
         <v>449</v>
@@ -3006,10 +3066,10 @@
         <v>4</v>
       </c>
       <c r="K16" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L16" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="M16" s="1">
         <v>496</v>
@@ -3029,7 +3089,7 @@
         <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" t="s">
         <v>193</v>
@@ -3038,7 +3098,7 @@
         <v>339</v>
       </c>
       <c r="G17" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H17" t="s">
         <v>450</v>
@@ -3050,10 +3110,10 @@
         <v>5</v>
       </c>
       <c r="K17" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L17" t="s">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="M17" s="1">
         <v>447</v>
@@ -3073,7 +3133,7 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E18" t="s">
         <v>194</v>
@@ -3082,7 +3142,7 @@
         <v>340</v>
       </c>
       <c r="G18" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H18" t="s">
         <v>450</v>
@@ -3097,7 +3157,7 @@
         <v>530</v>
       </c>
       <c r="L18" t="s">
-        <v>648</v>
+        <v>658</v>
       </c>
       <c r="M18" s="1">
         <v>307</v>
@@ -3108,7 +3168,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
         <v>3</v>
@@ -3117,16 +3177,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E19" t="s">
         <v>195</v>
       </c>
       <c r="F19" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G19" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H19" t="s">
         <v>450</v>
@@ -3141,10 +3201,10 @@
         <v>531</v>
       </c>
       <c r="L19" t="s">
-        <v>649</v>
+        <v>659</v>
       </c>
       <c r="M19" s="1">
-        <v>395</v>
+        <v>461</v>
       </c>
       <c r="N19" s="1">
         <v>473</v>
@@ -3152,7 +3212,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
@@ -3161,7 +3221,7 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E20" t="s">
         <v>196</v>
@@ -3170,7 +3230,7 @@
         <v>341</v>
       </c>
       <c r="G20" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H20" t="s">
         <v>450</v>
@@ -3185,10 +3245,10 @@
         <v>532</v>
       </c>
       <c r="L20" t="s">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="M20" s="1">
-        <v>473</v>
+        <v>395</v>
       </c>
       <c r="N20" s="1">
         <v>473</v>
@@ -3196,7 +3256,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -3205,7 +3265,7 @@
         <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E21" t="s">
         <v>197</v>
@@ -3214,7 +3274,7 @@
         <v>341</v>
       </c>
       <c r="G21" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H21" t="s">
         <v>450</v>
@@ -3229,10 +3289,10 @@
         <v>533</v>
       </c>
       <c r="L21" t="s">
-        <v>651</v>
+        <v>661</v>
       </c>
       <c r="M21" s="1">
-        <v>348</v>
+        <v>205</v>
       </c>
       <c r="N21" s="1">
         <v>473</v>
@@ -3249,7 +3309,7 @@
         <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E22" t="s">
         <v>198</v>
@@ -3258,7 +3318,7 @@
         <v>341</v>
       </c>
       <c r="G22" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H22" t="s">
         <v>450</v>
@@ -3273,7 +3333,7 @@
         <v>534</v>
       </c>
       <c r="L22" t="s">
-        <v>652</v>
+        <v>662</v>
       </c>
       <c r="M22" s="1">
         <v>410</v>
@@ -3284,7 +3344,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
@@ -3293,16 +3353,16 @@
         <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E23" t="s">
         <v>199</v>
       </c>
       <c r="F23" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G23" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H23" t="s">
         <v>450</v>
@@ -3317,10 +3377,10 @@
         <v>534</v>
       </c>
       <c r="L23" t="s">
-        <v>652</v>
+        <v>662</v>
       </c>
       <c r="M23" s="1">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="N23" s="1">
         <v>473</v>
@@ -3328,7 +3388,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
@@ -3343,10 +3403,10 @@
         <v>200</v>
       </c>
       <c r="F24" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G24" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H24" t="s">
         <v>450</v>
@@ -3358,13 +3418,13 @@
         <v>6</v>
       </c>
       <c r="K24" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L24" t="s">
-        <v>653</v>
+        <v>663</v>
       </c>
       <c r="M24" s="1">
-        <v>408</v>
+        <v>348</v>
       </c>
       <c r="N24" s="1">
         <v>473</v>
@@ -3372,7 +3432,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B25" t="s">
         <v>3</v>
@@ -3387,10 +3447,10 @@
         <v>201</v>
       </c>
       <c r="F25" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G25" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H25" t="s">
         <v>450</v>
@@ -3402,13 +3462,13 @@
         <v>6</v>
       </c>
       <c r="K25" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L25" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="M25" s="1">
-        <v>124</v>
+        <v>408</v>
       </c>
       <c r="N25" s="1">
         <v>473</v>
@@ -3416,7 +3476,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B26" t="s">
         <v>3</v>
@@ -3431,10 +3491,10 @@
         <v>202</v>
       </c>
       <c r="F26" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G26" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H26" t="s">
         <v>450</v>
@@ -3446,13 +3506,13 @@
         <v>6</v>
       </c>
       <c r="K26" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L26" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="M26" s="1">
-        <v>205</v>
+        <v>124</v>
       </c>
       <c r="N26" s="1">
         <v>473</v>
@@ -3475,10 +3535,10 @@
         <v>203</v>
       </c>
       <c r="F27" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G27" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H27" t="s">
         <v>451</v>
@@ -3490,10 +3550,10 @@
         <v>7</v>
       </c>
       <c r="K27" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L27" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="M27" s="1">
         <v>125</v>
@@ -3519,10 +3579,10 @@
         <v>204</v>
       </c>
       <c r="F28" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G28" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H28" t="s">
         <v>451</v>
@@ -3534,10 +3594,10 @@
         <v>7</v>
       </c>
       <c r="K28" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L28" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="M28" s="1">
         <v>201</v>
@@ -3563,10 +3623,10 @@
         <v>205</v>
       </c>
       <c r="F29" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G29" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H29" t="s">
         <v>451</v>
@@ -3581,7 +3641,7 @@
         <v>539</v>
       </c>
       <c r="L29" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="M29" s="1">
         <v>168</v>
@@ -3607,10 +3667,10 @@
         <v>206</v>
       </c>
       <c r="F30" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G30" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H30" t="s">
         <v>451</v>
@@ -3625,7 +3685,7 @@
         <v>540</v>
       </c>
       <c r="L30" t="s">
-        <v>657</v>
+        <v>668</v>
       </c>
       <c r="M30" s="1">
         <v>187</v>
@@ -3651,10 +3711,10 @@
         <v>207</v>
       </c>
       <c r="F31" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G31" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H31" t="s">
         <v>452</v>
@@ -3666,10 +3726,10 @@
         <v>8</v>
       </c>
       <c r="K31" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L31" t="s">
-        <v>658</v>
+        <v>668</v>
       </c>
       <c r="M31" s="1">
         <v>90</v>
@@ -3695,10 +3755,10 @@
         <v>208</v>
       </c>
       <c r="F32" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G32" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H32" t="s">
         <v>452</v>
@@ -3713,7 +3773,7 @@
         <v>541</v>
       </c>
       <c r="L32" t="s">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="M32" s="1">
         <v>57</v>
@@ -3739,10 +3799,10 @@
         <v>209</v>
       </c>
       <c r="F33" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G33" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H33" t="s">
         <v>452</v>
@@ -3754,10 +3814,10 @@
         <v>8</v>
       </c>
       <c r="K33" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="L33" t="s">
-        <v>659</v>
+        <v>669</v>
       </c>
       <c r="M33" s="1">
         <v>123</v>
@@ -3783,10 +3843,10 @@
         <v>210</v>
       </c>
       <c r="F34" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G34" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H34" t="s">
         <v>452</v>
@@ -3798,10 +3858,10 @@
         <v>8</v>
       </c>
       <c r="K34" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="L34" t="s">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="M34" s="1">
         <v>118</v>
@@ -3827,10 +3887,10 @@
         <v>211</v>
       </c>
       <c r="F35" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G35" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H35" t="s">
         <v>453</v>
@@ -3842,10 +3902,10 @@
         <v>9</v>
       </c>
       <c r="K35" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="L35" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="M35" s="1">
         <v>582</v>
@@ -3871,10 +3931,10 @@
         <v>212</v>
       </c>
       <c r="F36" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G36" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H36" t="s">
         <v>453</v>
@@ -3886,10 +3946,10 @@
         <v>9</v>
       </c>
       <c r="K36" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="L36" t="s">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="M36" s="1">
         <v>125</v>
@@ -3915,10 +3975,10 @@
         <v>213</v>
       </c>
       <c r="F37" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G37" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H37" t="s">
         <v>453</v>
@@ -3930,10 +3990,10 @@
         <v>9</v>
       </c>
       <c r="K37" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="L37" t="s">
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="M37" s="1">
         <v>170</v>
@@ -3959,10 +4019,10 @@
         <v>214</v>
       </c>
       <c r="F38" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G38" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H38" t="s">
         <v>453</v>
@@ -3974,10 +4034,10 @@
         <v>9</v>
       </c>
       <c r="K38" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="L38" t="s">
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="M38" s="1">
         <v>120</v>
@@ -4003,10 +4063,10 @@
         <v>215</v>
       </c>
       <c r="F39" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G39" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H39" t="s">
         <v>453</v>
@@ -4018,10 +4078,10 @@
         <v>9</v>
       </c>
       <c r="K39" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="L39" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="M39" s="1">
         <v>124</v>
@@ -4047,10 +4107,10 @@
         <v>216</v>
       </c>
       <c r="F40" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G40" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H40" t="s">
         <v>453</v>
@@ -4062,10 +4122,10 @@
         <v>9</v>
       </c>
       <c r="K40" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="L40" t="s">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="M40" s="1">
         <v>656</v>
@@ -4091,10 +4151,10 @@
         <v>217</v>
       </c>
       <c r="F41" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G41" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H41" t="s">
         <v>454</v>
@@ -4106,10 +4166,10 @@
         <v>10</v>
       </c>
       <c r="K41" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="L41" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="M41" s="1">
         <v>114</v>
@@ -4120,7 +4180,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="B42" t="s">
         <v>5</v>
@@ -4135,10 +4195,10 @@
         <v>218</v>
       </c>
       <c r="F42" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G42" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H42" t="s">
         <v>454</v>
@@ -4150,13 +4210,13 @@
         <v>10</v>
       </c>
       <c r="K42" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L42" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
       <c r="M42" s="1">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="N42" s="1">
         <v>114</v>
@@ -4164,7 +4224,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="B43" t="s">
         <v>5</v>
@@ -4179,10 +4239,10 @@
         <v>219</v>
       </c>
       <c r="F43" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G43" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H43" t="s">
         <v>454</v>
@@ -4194,13 +4254,13 @@
         <v>10</v>
       </c>
       <c r="K43" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L43" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="M43" s="1">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="N43" s="1">
         <v>114</v>
@@ -4208,7 +4268,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B44" t="s">
         <v>5</v>
@@ -4223,10 +4283,10 @@
         <v>220</v>
       </c>
       <c r="F44" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G44" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H44" t="s">
         <v>454</v>
@@ -4238,13 +4298,13 @@
         <v>10</v>
       </c>
       <c r="K44" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L44" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="M44" s="1">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="N44" s="1">
         <v>114</v>
@@ -4252,7 +4312,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="B45" t="s">
         <v>5</v>
@@ -4267,10 +4327,10 @@
         <v>221</v>
       </c>
       <c r="F45" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G45" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H45" t="s">
         <v>454</v>
@@ -4282,13 +4342,13 @@
         <v>10</v>
       </c>
       <c r="K45" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L45" t="s">
-        <v>667</v>
+        <v>678</v>
       </c>
       <c r="M45" s="1">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N45" s="1">
         <v>114</v>
@@ -4296,7 +4356,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B46" t="s">
         <v>5</v>
@@ -4311,10 +4371,10 @@
         <v>222</v>
       </c>
       <c r="F46" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G46" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H46" t="s">
         <v>454</v>
@@ -4326,13 +4386,13 @@
         <v>10</v>
       </c>
       <c r="K46" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L46" t="s">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="M46" s="1">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="N46" s="1">
         <v>114</v>
@@ -4340,7 +4400,7 @@
     </row>
     <row r="47">
       <c r="A47" s="1">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="B47" t="s">
         <v>5</v>
@@ -4355,10 +4415,10 @@
         <v>223</v>
       </c>
       <c r="F47" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G47" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H47" t="s">
         <v>454</v>
@@ -4370,13 +4430,13 @@
         <v>11</v>
       </c>
       <c r="K47" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="L47" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="M47" s="1">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="N47" s="1">
         <v>114</v>
@@ -4384,7 +4444,7 @@
     </row>
     <row r="48">
       <c r="A48" s="1">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B48" t="s">
         <v>5</v>
@@ -4399,10 +4459,10 @@
         <v>224</v>
       </c>
       <c r="F48" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G48" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H48" t="s">
         <v>454</v>
@@ -4414,13 +4474,13 @@
         <v>11</v>
       </c>
       <c r="K48" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="L48" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="M48" s="1">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="N48" s="1">
         <v>114</v>
@@ -4443,7 +4503,7 @@
         <v>225</v>
       </c>
       <c r="F49" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G49" t="s">
         <v>415</v>
@@ -4461,7 +4521,7 @@
         <v>554</v>
       </c>
       <c r="L49" t="s">
-        <v>669</v>
+        <v>682</v>
       </c>
       <c r="M49" s="1">
         <v>674</v>
@@ -4487,7 +4547,7 @@
         <v>226</v>
       </c>
       <c r="F50" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G50" t="s">
         <v>415</v>
@@ -4505,7 +4565,7 @@
         <v>555</v>
       </c>
       <c r="L50" t="s">
-        <v>670</v>
+        <v>683</v>
       </c>
       <c r="M50" s="1">
         <v>673</v>
@@ -4531,7 +4591,7 @@
         <v>227</v>
       </c>
       <c r="F51" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G51" t="s">
         <v>416</v>
@@ -4549,7 +4609,7 @@
         <v>556</v>
       </c>
       <c r="L51" t="s">
-        <v>671</v>
+        <v>684</v>
       </c>
       <c r="M51" s="1">
         <v>385</v>
@@ -4575,7 +4635,7 @@
         <v>228</v>
       </c>
       <c r="F52" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G52" t="s">
         <v>416</v>
@@ -4593,7 +4653,7 @@
         <v>557</v>
       </c>
       <c r="L52" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="M52" s="1">
         <v>452</v>
@@ -4619,7 +4679,7 @@
         <v>229</v>
       </c>
       <c r="F53" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G53" t="s">
         <v>417</v>
@@ -4634,10 +4694,10 @@
         <v>12</v>
       </c>
       <c r="K53" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L53" t="s">
-        <v>672</v>
+        <v>685</v>
       </c>
       <c r="M53" s="1">
         <v>440</v>
@@ -4663,7 +4723,7 @@
         <v>230</v>
       </c>
       <c r="F54" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G54" t="s">
         <v>418</v>
@@ -4678,10 +4738,10 @@
         <v>13</v>
       </c>
       <c r="K54" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="L54" t="s">
-        <v>672</v>
+        <v>686</v>
       </c>
       <c r="M54" s="1">
         <v>204</v>
@@ -4707,7 +4767,7 @@
         <v>231</v>
       </c>
       <c r="F55" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G55" t="s">
         <v>419</v>
@@ -4722,10 +4782,10 @@
         <v>13</v>
       </c>
       <c r="K55" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="L55" t="s">
-        <v>672</v>
+        <v>687</v>
       </c>
       <c r="M55" s="1">
         <v>57</v>
@@ -4751,7 +4811,7 @@
         <v>232</v>
       </c>
       <c r="F56" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G56" t="s">
         <v>419</v>
@@ -4766,10 +4826,10 @@
         <v>13</v>
       </c>
       <c r="K56" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L56" t="s">
-        <v>673</v>
+        <v>688</v>
       </c>
       <c r="M56" s="1">
         <v>108</v>
@@ -4795,7 +4855,7 @@
         <v>233</v>
       </c>
       <c r="F57" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G57" t="s">
         <v>419</v>
@@ -4810,10 +4870,10 @@
         <v>13</v>
       </c>
       <c r="K57" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="L57" t="s">
-        <v>674</v>
+        <v>689</v>
       </c>
       <c r="M57" s="1">
         <v>163</v>
@@ -4839,7 +4899,7 @@
         <v>234</v>
       </c>
       <c r="F58" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G58" t="s">
         <v>419</v>
@@ -4854,10 +4914,10 @@
         <v>13</v>
       </c>
       <c r="K58" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="L58" t="s">
-        <v>675</v>
+        <v>690</v>
       </c>
       <c r="M58" s="1">
         <v>132</v>
@@ -4883,7 +4943,7 @@
         <v>235</v>
       </c>
       <c r="F59" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G59" t="s">
         <v>419</v>
@@ -4898,10 +4958,10 @@
         <v>14</v>
       </c>
       <c r="K59" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="L59" t="s">
-        <v>676</v>
+        <v>690</v>
       </c>
       <c r="M59" s="1">
         <v>429</v>
@@ -4927,7 +4987,7 @@
         <v>236</v>
       </c>
       <c r="F60" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G60" t="s">
         <v>420</v>
@@ -4942,10 +5002,10 @@
         <v>14</v>
       </c>
       <c r="K60" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="L60" t="s">
-        <v>676</v>
+        <v>690</v>
       </c>
       <c r="M60" s="1">
         <v>227</v>
@@ -4971,7 +5031,7 @@
         <v>237</v>
       </c>
       <c r="F61" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G61" t="s">
         <v>420</v>
@@ -4986,10 +5046,10 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="L61" t="s">
-        <v>677</v>
+        <v>691</v>
       </c>
       <c r="M61" s="1">
         <v>107</v>
@@ -5015,7 +5075,7 @@
         <v>238</v>
       </c>
       <c r="F62" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G62" t="s">
         <v>420</v>
@@ -5030,10 +5090,10 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="L62" t="s">
-        <v>678</v>
+        <v>692</v>
       </c>
       <c r="M62" s="1">
         <v>156</v>
@@ -5059,7 +5119,7 @@
         <v>239</v>
       </c>
       <c r="F63" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G63" t="s">
         <v>420</v>
@@ -5074,10 +5134,10 @@
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="L63" t="s">
-        <v>679</v>
+        <v>693</v>
       </c>
       <c r="M63" s="1">
         <v>37</v>
@@ -5103,7 +5163,7 @@
         <v>240</v>
       </c>
       <c r="F64" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G64" t="s">
         <v>420</v>
@@ -5118,10 +5178,10 @@
         <v>16</v>
       </c>
       <c r="K64" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="L64" t="s">
-        <v>679</v>
+        <v>694</v>
       </c>
       <c r="M64" s="1">
         <v>208</v>
@@ -5147,7 +5207,7 @@
         <v>241</v>
       </c>
       <c r="F65" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G65" t="s">
         <v>421</v>
@@ -5162,10 +5222,10 @@
         <v>16</v>
       </c>
       <c r="K65" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="L65" t="s">
-        <v>680</v>
+        <v>694</v>
       </c>
       <c r="M65" s="1">
         <v>124</v>
@@ -5191,7 +5251,7 @@
         <v>242</v>
       </c>
       <c r="F66" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G66" t="s">
         <v>421</v>
@@ -5206,10 +5266,10 @@
         <v>16</v>
       </c>
       <c r="K66" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="L66" t="s">
-        <v>681</v>
+        <v>695</v>
       </c>
       <c r="M66" s="1">
         <v>161</v>
@@ -5235,7 +5295,7 @@
         <v>243</v>
       </c>
       <c r="F67" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G67" t="s">
         <v>421</v>
@@ -5250,10 +5310,10 @@
         <v>16</v>
       </c>
       <c r="K67" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="L67" t="s">
-        <v>682</v>
+        <v>696</v>
       </c>
       <c r="M67" s="1">
         <v>113</v>
@@ -5279,7 +5339,7 @@
         <v>244</v>
       </c>
       <c r="F68" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G68" t="s">
         <v>422</v>
@@ -5294,10 +5354,10 @@
         <v>17</v>
       </c>
       <c r="K68" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="L68" t="s">
-        <v>683</v>
+        <v>697</v>
       </c>
       <c r="M68" s="1">
         <v>66</v>
@@ -5323,7 +5383,7 @@
         <v>245</v>
       </c>
       <c r="F69" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G69" t="s">
         <v>423</v>
@@ -5338,10 +5398,10 @@
         <v>17</v>
       </c>
       <c r="K69" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="L69" t="s">
-        <v>683</v>
+        <v>697</v>
       </c>
       <c r="M69" s="1">
         <v>112</v>
@@ -5367,7 +5427,7 @@
         <v>246</v>
       </c>
       <c r="F70" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G70" t="s">
         <v>423</v>
@@ -5382,10 +5442,10 @@
         <v>17</v>
       </c>
       <c r="K70" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="L70" t="s">
-        <v>684</v>
+        <v>698</v>
       </c>
       <c r="M70" s="1">
         <v>65</v>
@@ -5411,7 +5471,7 @@
         <v>247</v>
       </c>
       <c r="F71" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G71" t="s">
         <v>423</v>
@@ -5426,10 +5486,10 @@
         <v>17</v>
       </c>
       <c r="K71" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="L71" t="s">
-        <v>685</v>
+        <v>699</v>
       </c>
       <c r="M71" s="1">
         <v>111</v>
@@ -5455,7 +5515,7 @@
         <v>248</v>
       </c>
       <c r="F72" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G72" t="s">
         <v>423</v>
@@ -5470,10 +5530,10 @@
         <v>17</v>
       </c>
       <c r="K72" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="L72" t="s">
-        <v>685</v>
+        <v>700</v>
       </c>
       <c r="M72" s="1">
         <v>62</v>
@@ -5499,7 +5559,7 @@
         <v>249</v>
       </c>
       <c r="F73" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G73" t="s">
         <v>423</v>
@@ -5514,10 +5574,10 @@
         <v>18</v>
       </c>
       <c r="K73" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="L73" t="s">
-        <v>685</v>
+        <v>701</v>
       </c>
       <c r="M73" s="1">
         <v>104</v>
@@ -5543,7 +5603,7 @@
         <v>250</v>
       </c>
       <c r="F74" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G74" t="s">
         <v>423</v>
@@ -5558,10 +5618,10 @@
         <v>18</v>
       </c>
       <c r="K74" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="L74" t="s">
-        <v>685</v>
+        <v>702</v>
       </c>
       <c r="M74" s="1">
         <v>97</v>
@@ -5587,7 +5647,7 @@
         <v>251</v>
       </c>
       <c r="F75" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G75" t="s">
         <v>424</v>
@@ -5602,10 +5662,10 @@
         <v>18</v>
       </c>
       <c r="K75" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="L75" t="s">
-        <v>686</v>
+        <v>703</v>
       </c>
       <c r="M75" s="1">
         <v>135</v>
@@ -5631,7 +5691,7 @@
         <v>252</v>
       </c>
       <c r="F76" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G76" t="s">
         <v>425</v>
@@ -5646,10 +5706,10 @@
         <v>18</v>
       </c>
       <c r="K76" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="L76" t="s">
-        <v>687</v>
+        <v>704</v>
       </c>
       <c r="M76" s="1">
         <v>127</v>
@@ -5675,7 +5735,7 @@
         <v>253</v>
       </c>
       <c r="F77" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G77" t="s">
         <v>425</v>
@@ -5690,10 +5750,10 @@
         <v>18</v>
       </c>
       <c r="K77" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="L77" t="s">
-        <v>687</v>
+        <v>705</v>
       </c>
       <c r="M77" s="1">
         <v>197</v>
@@ -5719,7 +5779,7 @@
         <v>254</v>
       </c>
       <c r="F78" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G78" t="s">
         <v>425</v>
@@ -5734,10 +5794,10 @@
         <v>19</v>
       </c>
       <c r="K78" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="L78" t="s">
-        <v>688</v>
+        <v>706</v>
       </c>
       <c r="M78" s="1">
         <v>45</v>
@@ -5763,7 +5823,7 @@
         <v>255</v>
       </c>
       <c r="F79" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G79" t="s">
         <v>425</v>
@@ -5778,10 +5838,10 @@
         <v>19</v>
       </c>
       <c r="K79" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="L79" t="s">
-        <v>689</v>
+        <v>707</v>
       </c>
       <c r="M79" s="1">
         <v>41</v>
@@ -5807,7 +5867,7 @@
         <v>256</v>
       </c>
       <c r="F80" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G80" t="s">
         <v>425</v>
@@ -5822,10 +5882,10 @@
         <v>19</v>
       </c>
       <c r="K80" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="L80" t="s">
-        <v>689</v>
+        <v>708</v>
       </c>
       <c r="M80" s="1">
         <v>84</v>
@@ -5851,7 +5911,7 @@
         <v>257</v>
       </c>
       <c r="F81" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G81" t="s">
         <v>425</v>
@@ -5866,10 +5926,10 @@
         <v>19</v>
       </c>
       <c r="K81" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="L81" t="s">
-        <v>690</v>
+        <v>709</v>
       </c>
       <c r="M81" s="1">
         <v>79</v>
@@ -5895,7 +5955,7 @@
         <v>258</v>
       </c>
       <c r="F82" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G82" t="s">
         <v>425</v>
@@ -5910,10 +5970,10 @@
         <v>19</v>
       </c>
       <c r="K82" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="L82" t="s">
-        <v>691</v>
+        <v>710</v>
       </c>
       <c r="M82" s="1">
         <v>58</v>
@@ -5939,7 +5999,7 @@
         <v>259</v>
       </c>
       <c r="F83" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G83" t="s">
         <v>425</v>
@@ -5954,10 +6014,10 @@
         <v>20</v>
       </c>
       <c r="K83" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="L83" t="s">
-        <v>691</v>
+        <v>711</v>
       </c>
       <c r="M83" s="1">
         <v>320</v>
@@ -5983,7 +6043,7 @@
         <v>260</v>
       </c>
       <c r="F84" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G84" t="s">
         <v>425</v>
@@ -6001,7 +6061,7 @@
         <v>583</v>
       </c>
       <c r="L84" t="s">
-        <v>691</v>
+        <v>712</v>
       </c>
       <c r="M84" s="1">
         <v>496</v>
@@ -6027,7 +6087,7 @@
         <v>261</v>
       </c>
       <c r="F85" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G85" t="s">
         <v>426</v>
@@ -6042,10 +6102,10 @@
         <v>20</v>
       </c>
       <c r="K85" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="L85" t="s">
-        <v>692</v>
+        <v>712</v>
       </c>
       <c r="M85" s="1">
         <v>361</v>
@@ -6071,7 +6131,7 @@
         <v>262</v>
       </c>
       <c r="F86" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G86" t="s">
         <v>427</v>
@@ -6086,10 +6146,10 @@
         <v>20</v>
       </c>
       <c r="K86" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="L86" t="s">
-        <v>693</v>
+        <v>713</v>
       </c>
       <c r="M86" s="1">
         <v>329</v>
@@ -6115,7 +6175,7 @@
         <v>263</v>
       </c>
       <c r="F87" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G87" t="s">
         <v>427</v>
@@ -6130,10 +6190,10 @@
         <v>21</v>
       </c>
       <c r="K87" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="L87" t="s">
-        <v>694</v>
+        <v>713</v>
       </c>
       <c r="M87" s="1">
         <v>92</v>
@@ -6159,7 +6219,7 @@
         <v>264</v>
       </c>
       <c r="F88" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G88" t="s">
         <v>427</v>
@@ -6174,10 +6234,10 @@
         <v>21</v>
       </c>
       <c r="K88" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="L88" t="s">
-        <v>695</v>
+        <v>714</v>
       </c>
       <c r="M88" s="1">
         <v>233</v>
@@ -6203,7 +6263,7 @@
         <v>265</v>
       </c>
       <c r="F89" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G89" t="s">
         <v>427</v>
@@ -6221,7 +6281,7 @@
         <v>587</v>
       </c>
       <c r="L89" t="s">
-        <v>696</v>
+        <v>715</v>
       </c>
       <c r="M89" s="1">
         <v>48</v>
@@ -6247,7 +6307,7 @@
         <v>266</v>
       </c>
       <c r="F90" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G90" t="s">
         <v>427</v>
@@ -6265,7 +6325,7 @@
         <v>588</v>
       </c>
       <c r="L90" t="s">
-        <v>697</v>
+        <v>715</v>
       </c>
       <c r="M90" s="1">
         <v>73</v>
@@ -6291,7 +6351,7 @@
         <v>267</v>
       </c>
       <c r="F91" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G91" t="s">
         <v>427</v>
@@ -6306,10 +6366,10 @@
         <v>21</v>
       </c>
       <c r="K91" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="L91" t="s">
-        <v>698</v>
+        <v>716</v>
       </c>
       <c r="M91" s="1">
         <v>188</v>
@@ -6335,7 +6395,7 @@
         <v>268</v>
       </c>
       <c r="F92" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G92" t="s">
         <v>427</v>
@@ -6350,10 +6410,10 @@
         <v>22</v>
       </c>
       <c r="K92" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="L92" t="s">
-        <v>699</v>
+        <v>717</v>
       </c>
       <c r="M92" s="1">
         <v>193</v>
@@ -6379,7 +6439,7 @@
         <v>269</v>
       </c>
       <c r="F93" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G93" t="s">
         <v>427</v>
@@ -6394,10 +6454,10 @@
         <v>22</v>
       </c>
       <c r="K93" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="L93" t="s">
-        <v>700</v>
+        <v>718</v>
       </c>
       <c r="M93" s="1">
         <v>125</v>
@@ -6423,7 +6483,7 @@
         <v>270</v>
       </c>
       <c r="F94" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G94" t="s">
         <v>428</v>
@@ -6438,10 +6498,10 @@
         <v>22</v>
       </c>
       <c r="K94" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="L94" t="s">
-        <v>701</v>
+        <v>719</v>
       </c>
       <c r="M94" s="1">
         <v>188</v>
@@ -6467,7 +6527,7 @@
         <v>271</v>
       </c>
       <c r="F95" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G95" t="s">
         <v>429</v>
@@ -6482,10 +6542,10 @@
         <v>23</v>
       </c>
       <c r="K95" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L95" t="s">
-        <v>702</v>
+        <v>720</v>
       </c>
       <c r="M95" s="1">
         <v>69</v>
@@ -6511,7 +6571,7 @@
         <v>272</v>
       </c>
       <c r="F96" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G96" t="s">
         <v>429</v>
@@ -6526,10 +6586,10 @@
         <v>23</v>
       </c>
       <c r="K96" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="L96" t="s">
-        <v>703</v>
+        <v>720</v>
       </c>
       <c r="M96" s="1">
         <v>119</v>
@@ -6555,7 +6615,7 @@
         <v>273</v>
       </c>
       <c r="F97" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G97" t="s">
         <v>429</v>
@@ -6570,10 +6630,10 @@
         <v>23</v>
       </c>
       <c r="K97" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="L97" t="s">
-        <v>704</v>
+        <v>721</v>
       </c>
       <c r="M97" s="1">
         <v>71</v>
@@ -6599,7 +6659,7 @@
         <v>274</v>
       </c>
       <c r="F98" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G98" t="s">
         <v>429</v>
@@ -6614,10 +6674,10 @@
         <v>24</v>
       </c>
       <c r="K98" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="L98" t="s">
-        <v>704</v>
+        <v>721</v>
       </c>
       <c r="M98" s="1">
         <v>196</v>
@@ -6643,7 +6703,7 @@
         <v>275</v>
       </c>
       <c r="F99" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G99" t="s">
         <v>429</v>
@@ -6658,10 +6718,10 @@
         <v>24</v>
       </c>
       <c r="K99" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="L99" t="s">
-        <v>705</v>
+        <v>722</v>
       </c>
       <c r="M99" s="1">
         <v>181</v>
@@ -6687,7 +6747,7 @@
         <v>276</v>
       </c>
       <c r="F100" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G100" t="s">
         <v>429</v>
@@ -6702,10 +6762,10 @@
         <v>25</v>
       </c>
       <c r="K100" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="L100" t="s">
-        <v>705</v>
+        <v>723</v>
       </c>
       <c r="M100" s="1">
         <v>141</v>
@@ -6731,7 +6791,7 @@
         <v>277</v>
       </c>
       <c r="F101" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G101" t="s">
         <v>429</v>
@@ -6746,10 +6806,10 @@
         <v>25</v>
       </c>
       <c r="K101" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="L101" t="s">
-        <v>706</v>
+        <v>724</v>
       </c>
       <c r="M101" s="1">
         <v>159</v>
@@ -6775,7 +6835,7 @@
         <v>278</v>
       </c>
       <c r="F102" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G102" t="s">
         <v>430</v>
@@ -6790,10 +6850,10 @@
         <v>25</v>
       </c>
       <c r="K102" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="L102" t="s">
-        <v>707</v>
+        <v>725</v>
       </c>
       <c r="M102" s="1">
         <v>125</v>
@@ -6819,7 +6879,7 @@
         <v>279</v>
       </c>
       <c r="F103" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G103" t="s">
         <v>431</v>
@@ -6834,10 +6894,10 @@
         <v>26</v>
       </c>
       <c r="K103" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="L103" t="s">
-        <v>707</v>
+        <v>726</v>
       </c>
       <c r="M103" s="1">
         <v>198</v>
@@ -6863,7 +6923,7 @@
         <v>280</v>
       </c>
       <c r="F104" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G104" t="s">
         <v>431</v>
@@ -6878,10 +6938,10 @@
         <v>26</v>
       </c>
       <c r="K104" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="L104" t="s">
-        <v>708</v>
+        <v>726</v>
       </c>
       <c r="M104" s="1">
         <v>156</v>
@@ -6907,7 +6967,7 @@
         <v>281</v>
       </c>
       <c r="F105" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G105" t="s">
         <v>431</v>
@@ -6922,10 +6982,10 @@
         <v>26</v>
       </c>
       <c r="K105" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="L105" t="s">
-        <v>709</v>
+        <v>727</v>
       </c>
       <c r="M105" s="1">
         <v>353</v>
@@ -6951,7 +7011,7 @@
         <v>282</v>
       </c>
       <c r="F106" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G106" t="s">
         <v>431</v>
@@ -6966,10 +7026,10 @@
         <v>26</v>
       </c>
       <c r="K106" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="L106" t="s">
-        <v>710</v>
+        <v>728</v>
       </c>
       <c r="M106" s="1">
         <v>250</v>
@@ -6995,7 +7055,7 @@
         <v>283</v>
       </c>
       <c r="F107" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G107" t="s">
         <v>431</v>
@@ -7010,10 +7070,10 @@
         <v>27</v>
       </c>
       <c r="K107" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="L107" t="s">
-        <v>711</v>
+        <v>729</v>
       </c>
       <c r="M107" s="1">
         <v>49</v>
@@ -7039,7 +7099,7 @@
         <v>284</v>
       </c>
       <c r="F108" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G108" t="s">
         <v>431</v>
@@ -7057,7 +7117,7 @@
         <v>602</v>
       </c>
       <c r="L108" t="s">
-        <v>711</v>
+        <v>730</v>
       </c>
       <c r="M108" s="1">
         <v>140</v>
@@ -7083,7 +7143,7 @@
         <v>285</v>
       </c>
       <c r="F109" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G109" t="s">
         <v>431</v>
@@ -7101,7 +7161,7 @@
         <v>603</v>
       </c>
       <c r="L109" t="s">
-        <v>712</v>
+        <v>731</v>
       </c>
       <c r="M109" s="1">
         <v>89</v>
@@ -7127,7 +7187,7 @@
         <v>286</v>
       </c>
       <c r="F110" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G110" t="s">
         <v>431</v>
@@ -7142,10 +7202,10 @@
         <v>27</v>
       </c>
       <c r="K110" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L110" t="s">
-        <v>713</v>
+        <v>732</v>
       </c>
       <c r="M110" s="1">
         <v>51</v>
@@ -7171,7 +7231,7 @@
         <v>287</v>
       </c>
       <c r="F111" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G111" t="s">
         <v>432</v>
@@ -7189,7 +7249,7 @@
         <v>604</v>
       </c>
       <c r="L111" t="s">
-        <v>714</v>
+        <v>733</v>
       </c>
       <c r="M111" s="1">
         <v>132</v>
@@ -7215,7 +7275,7 @@
         <v>288</v>
       </c>
       <c r="F112" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G112" t="s">
         <v>433</v>
@@ -7230,10 +7290,10 @@
         <v>28</v>
       </c>
       <c r="K112" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L112" t="s">
-        <v>715</v>
+        <v>734</v>
       </c>
       <c r="M112" s="1">
         <v>182</v>
@@ -7259,7 +7319,7 @@
         <v>289</v>
       </c>
       <c r="F113" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G113" t="s">
         <v>433</v>
@@ -7274,10 +7334,10 @@
         <v>28</v>
       </c>
       <c r="K113" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="L113" t="s">
-        <v>716</v>
+        <v>735</v>
       </c>
       <c r="M113" s="1">
         <v>285</v>
@@ -7303,7 +7363,7 @@
         <v>290</v>
       </c>
       <c r="F114" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G114" t="s">
         <v>433</v>
@@ -7318,10 +7378,10 @@
         <v>28</v>
       </c>
       <c r="K114" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="L114" t="s">
-        <v>717</v>
+        <v>736</v>
       </c>
       <c r="M114" s="1">
         <v>366</v>
@@ -7347,7 +7407,7 @@
         <v>291</v>
       </c>
       <c r="F115" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G115" t="s">
         <v>434</v>
@@ -7365,7 +7425,7 @@
         <v>607</v>
       </c>
       <c r="L115" t="s">
-        <v>717</v>
+        <v>736</v>
       </c>
       <c r="M115" s="1">
         <v>213</v>
@@ -7391,7 +7451,7 @@
         <v>292</v>
       </c>
       <c r="F116" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G116" t="s">
         <v>434</v>
@@ -7406,10 +7466,10 @@
         <v>29</v>
       </c>
       <c r="K116" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L116" t="s">
-        <v>717</v>
+        <v>737</v>
       </c>
       <c r="M116" s="1">
         <v>101</v>
@@ -7435,7 +7495,7 @@
         <v>293</v>
       </c>
       <c r="F117" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G117" t="s">
         <v>435</v>
@@ -7450,10 +7510,10 @@
         <v>29</v>
       </c>
       <c r="K117" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L117" t="s">
-        <v>718</v>
+        <v>738</v>
       </c>
       <c r="M117" s="1">
         <v>155</v>
@@ -7479,7 +7539,7 @@
         <v>294</v>
       </c>
       <c r="F118" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G118" t="s">
         <v>435</v>
@@ -7494,10 +7554,10 @@
         <v>29</v>
       </c>
       <c r="K118" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L118" t="s">
-        <v>719</v>
+        <v>738</v>
       </c>
       <c r="M118" s="1">
         <v>70</v>
@@ -7523,7 +7583,7 @@
         <v>295</v>
       </c>
       <c r="F119" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G119" t="s">
         <v>435</v>
@@ -7538,10 +7598,10 @@
         <v>29</v>
       </c>
       <c r="K119" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L119" t="s">
-        <v>720</v>
+        <v>739</v>
       </c>
       <c r="M119" s="1">
         <v>116</v>
@@ -7567,7 +7627,7 @@
         <v>296</v>
       </c>
       <c r="F120" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G120" t="s">
         <v>435</v>
@@ -7582,10 +7642,10 @@
         <v>30</v>
       </c>
       <c r="K120" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L120" t="s">
-        <v>721</v>
+        <v>740</v>
       </c>
       <c r="M120" s="1">
         <v>132</v>
@@ -7611,7 +7671,7 @@
         <v>297</v>
       </c>
       <c r="F121" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G121" t="s">
         <v>435</v>
@@ -7626,10 +7686,10 @@
         <v>30</v>
       </c>
       <c r="K121" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L121" t="s">
-        <v>722</v>
+        <v>741</v>
       </c>
       <c r="M121" s="1">
         <v>251</v>
@@ -7655,7 +7715,7 @@
         <v>298</v>
       </c>
       <c r="F122" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G122" t="s">
         <v>436</v>
@@ -7670,10 +7730,10 @@
         <v>30</v>
       </c>
       <c r="K122" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L122" t="s">
-        <v>722</v>
+        <v>741</v>
       </c>
       <c r="M122" s="1">
         <v>416</v>
@@ -7699,7 +7759,7 @@
         <v>299</v>
       </c>
       <c r="F123" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G123" t="s">
         <v>437</v>
@@ -7714,10 +7774,10 @@
         <v>30</v>
       </c>
       <c r="K123" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L123" t="s">
-        <v>723</v>
+        <v>742</v>
       </c>
       <c r="M123" s="1">
         <v>198</v>
@@ -7743,7 +7803,7 @@
         <v>300</v>
       </c>
       <c r="F124" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G124" t="s">
         <v>437</v>
@@ -7761,7 +7821,7 @@
         <v>615</v>
       </c>
       <c r="L124" t="s">
-        <v>724</v>
+        <v>742</v>
       </c>
       <c r="M124" s="1">
         <v>95</v>
@@ -7787,7 +7847,7 @@
         <v>301</v>
       </c>
       <c r="F125" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G125" t="s">
         <v>437</v>
@@ -7802,10 +7862,10 @@
         <v>31</v>
       </c>
       <c r="K125" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L125" t="s">
-        <v>724</v>
+        <v>743</v>
       </c>
       <c r="M125" s="1">
         <v>108</v>
@@ -7831,7 +7891,7 @@
         <v>302</v>
       </c>
       <c r="F126" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G126" t="s">
         <v>437</v>
@@ -7846,10 +7906,10 @@
         <v>31</v>
       </c>
       <c r="K126" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L126" t="s">
-        <v>725</v>
+        <v>744</v>
       </c>
       <c r="M126" s="1">
         <v>111</v>
@@ -7875,7 +7935,7 @@
         <v>303</v>
       </c>
       <c r="F127" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G127" t="s">
         <v>437</v>
@@ -7890,10 +7950,10 @@
         <v>31</v>
       </c>
       <c r="K127" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L127" t="s">
-        <v>725</v>
+        <v>744</v>
       </c>
       <c r="M127" s="1">
         <v>113</v>
@@ -7919,7 +7979,7 @@
         <v>304</v>
       </c>
       <c r="F128" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G128" t="s">
         <v>437</v>
@@ -7934,10 +7994,10 @@
         <v>32</v>
       </c>
       <c r="K128" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="L128" t="s">
-        <v>725</v>
+        <v>745</v>
       </c>
       <c r="M128" s="1">
         <v>102</v>
@@ -7963,7 +8023,7 @@
         <v>305</v>
       </c>
       <c r="F129" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G129" t="s">
         <v>437</v>
@@ -7978,10 +8038,10 @@
         <v>32</v>
       </c>
       <c r="K129" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="L129" t="s">
-        <v>726</v>
+        <v>746</v>
       </c>
       <c r="M129" s="1">
         <v>175</v>
@@ -8007,7 +8067,7 @@
         <v>306</v>
       </c>
       <c r="F130" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G130" t="s">
         <v>437</v>
@@ -8022,10 +8082,10 @@
         <v>32</v>
       </c>
       <c r="K130" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="L130" t="s">
-        <v>727</v>
+        <v>747</v>
       </c>
       <c r="M130" s="1">
         <v>145</v>
@@ -8051,7 +8111,7 @@
         <v>307</v>
       </c>
       <c r="F131" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G131" t="s">
         <v>438</v>
@@ -8066,10 +8126,10 @@
         <v>32</v>
       </c>
       <c r="K131" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="L131" t="s">
-        <v>728</v>
+        <v>748</v>
       </c>
       <c r="M131" s="1">
         <v>208</v>
@@ -8095,7 +8155,7 @@
         <v>308</v>
       </c>
       <c r="F132" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G132" t="s">
         <v>439</v>
@@ -8110,10 +8170,10 @@
         <v>33</v>
       </c>
       <c r="K132" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L132" t="s">
-        <v>729</v>
+        <v>748</v>
       </c>
       <c r="M132" s="1">
         <v>42</v>
@@ -8139,7 +8199,7 @@
         <v>309</v>
       </c>
       <c r="F133" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G133" t="s">
         <v>439</v>
@@ -8154,10 +8214,10 @@
         <v>33</v>
       </c>
       <c r="K133" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L133" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="M133" s="1">
         <v>38</v>
@@ -8183,7 +8243,7 @@
         <v>310</v>
       </c>
       <c r="F134" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G134" t="s">
         <v>439</v>
@@ -8198,10 +8258,10 @@
         <v>33</v>
       </c>
       <c r="K134" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L134" t="s">
-        <v>731</v>
+        <v>750</v>
       </c>
       <c r="M134" s="1">
         <v>34</v>
@@ -8227,7 +8287,7 @@
         <v>311</v>
       </c>
       <c r="F135" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G135" t="s">
         <v>439</v>
@@ -8242,10 +8302,10 @@
         <v>33</v>
       </c>
       <c r="K135" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L135" t="s">
-        <v>731</v>
+        <v>751</v>
       </c>
       <c r="M135" s="1">
         <v>45</v>
@@ -8271,7 +8331,7 @@
         <v>312</v>
       </c>
       <c r="F136" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G136" t="s">
         <v>439</v>
@@ -8286,10 +8346,10 @@
         <v>34</v>
       </c>
       <c r="K136" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="L136" t="s">
-        <v>731</v>
+        <v>752</v>
       </c>
       <c r="M136" s="1">
         <v>131</v>
@@ -8315,7 +8375,7 @@
         <v>313</v>
       </c>
       <c r="F137" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G137" t="s">
         <v>439</v>
@@ -8330,10 +8390,10 @@
         <v>34</v>
       </c>
       <c r="K137" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="L137" t="s">
-        <v>732</v>
+        <v>753</v>
       </c>
       <c r="M137" s="1">
         <v>375</v>
@@ -8359,7 +8419,7 @@
         <v>314</v>
       </c>
       <c r="F138" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G138" t="s">
         <v>439</v>
@@ -8374,10 +8434,10 @@
         <v>34</v>
       </c>
       <c r="K138" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L138" t="s">
-        <v>732</v>
+        <v>754</v>
       </c>
       <c r="M138" s="1">
         <v>125</v>
@@ -8403,7 +8463,7 @@
         <v>315</v>
       </c>
       <c r="F139" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G139" t="s">
         <v>439</v>
@@ -8418,10 +8478,10 @@
         <v>34</v>
       </c>
       <c r="K139" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="L139" t="s">
-        <v>733</v>
+        <v>755</v>
       </c>
       <c r="M139" s="1">
         <v>296</v>
@@ -8447,7 +8507,7 @@
         <v>316</v>
       </c>
       <c r="F140" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G140" t="s">
         <v>440</v>
@@ -8462,10 +8522,10 @@
         <v>34</v>
       </c>
       <c r="K140" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="L140" t="s">
-        <v>734</v>
+        <v>755</v>
       </c>
       <c r="M140" s="1">
         <v>277</v>
@@ -8491,7 +8551,7 @@
         <v>317</v>
       </c>
       <c r="F141" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G141" t="s">
         <v>441</v>
@@ -8506,10 +8566,10 @@
         <v>35</v>
       </c>
       <c r="K141" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L141" t="s">
-        <v>735</v>
+        <v>755</v>
       </c>
       <c r="M141" s="1">
         <v>81</v>
@@ -8535,7 +8595,7 @@
         <v>318</v>
       </c>
       <c r="F142" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G142" t="s">
         <v>441</v>
@@ -8550,10 +8610,10 @@
         <v>35</v>
       </c>
       <c r="K142" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="L142" t="s">
-        <v>736</v>
+        <v>755</v>
       </c>
       <c r="M142" s="1">
         <v>83</v>
@@ -8579,7 +8639,7 @@
         <v>319</v>
       </c>
       <c r="F143" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G143" t="s">
         <v>441</v>
@@ -8594,10 +8654,10 @@
         <v>35</v>
       </c>
       <c r="K143" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L143" t="s">
-        <v>737</v>
+        <v>756</v>
       </c>
       <c r="M143" s="1">
         <v>75</v>
@@ -8623,7 +8683,7 @@
         <v>320</v>
       </c>
       <c r="F144" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G144" t="s">
         <v>441</v>
@@ -8638,10 +8698,10 @@
         <v>35</v>
       </c>
       <c r="K144" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L144" t="s">
-        <v>738</v>
+        <v>756</v>
       </c>
       <c r="M144" s="1">
         <v>120</v>
@@ -8667,7 +8727,7 @@
         <v>321</v>
       </c>
       <c r="F145" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G145" t="s">
         <v>441</v>
@@ -8682,10 +8742,10 @@
         <v>35</v>
       </c>
       <c r="K145" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L145" t="s">
-        <v>739</v>
+        <v>757</v>
       </c>
       <c r="M145" s="1">
         <v>75</v>
@@ -8711,7 +8771,7 @@
         <v>322</v>
       </c>
       <c r="F146" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G146" t="s">
         <v>442</v>
@@ -8726,10 +8786,10 @@
         <v>36</v>
       </c>
       <c r="K146" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L146" t="s">
-        <v>740</v>
+        <v>757</v>
       </c>
       <c r="M146" s="1">
         <v>212</v>
@@ -8755,7 +8815,7 @@
         <v>323</v>
       </c>
       <c r="F147" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G147" t="s">
         <v>443</v>
@@ -8770,10 +8830,10 @@
         <v>36</v>
       </c>
       <c r="K147" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L147" t="s">
-        <v>741</v>
+        <v>758</v>
       </c>
       <c r="M147" s="1">
         <v>166</v>
@@ -8799,7 +8859,7 @@
         <v>324</v>
       </c>
       <c r="F148" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G148" t="s">
         <v>443</v>
@@ -8814,10 +8874,10 @@
         <v>36</v>
       </c>
       <c r="K148" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="L148" t="s">
-        <v>742</v>
+        <v>759</v>
       </c>
       <c r="M148" s="1">
         <v>145</v>
@@ -8843,7 +8903,7 @@
         <v>325</v>
       </c>
       <c r="F149" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="G149" t="s">
         <v>443</v>
@@ -8858,10 +8918,10 @@
         <v>36</v>
       </c>
       <c r="K149" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L149" t="s">
-        <v>743</v>
+        <v>760</v>
       </c>
       <c r="M149" s="1">
         <v>109</v>
@@ -8887,7 +8947,7 @@
         <v>326</v>
       </c>
       <c r="F150" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="G150" t="s">
         <v>443</v>
@@ -8902,10 +8962,10 @@
         <v>36</v>
       </c>
       <c r="K150" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L150" t="s">
-        <v>744</v>
+        <v>761</v>
       </c>
       <c r="M150" s="1">
         <v>108</v>
@@ -8931,7 +8991,7 @@
         <v>327</v>
       </c>
       <c r="F151" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="G151" t="s">
         <v>443</v>
@@ -8946,10 +9006,10 @@
         <v>36</v>
       </c>
       <c r="K151" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L151" t="s">
-        <v>745</v>
+        <v>762</v>
       </c>
       <c r="M151" s="1">
         <v>91</v>
@@ -8975,7 +9035,7 @@
         <v>328</v>
       </c>
       <c r="F152" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G152" t="s">
         <v>444</v>
@@ -8990,10 +9050,10 @@
         <v>37</v>
       </c>
       <c r="K152" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="L152" t="s">
-        <v>745</v>
+        <v>763</v>
       </c>
       <c r="M152" s="1">
         <v>50</v>
@@ -9019,7 +9079,7 @@
         <v>329</v>
       </c>
       <c r="F153" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G153" t="s">
         <v>445</v>
@@ -9034,10 +9094,10 @@
         <v>37</v>
       </c>
       <c r="K153" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="L153" t="s">
-        <v>746</v>
+        <v>764</v>
       </c>
       <c r="M153" s="1">
         <v>88</v>
@@ -9063,7 +9123,7 @@
         <v>330</v>
       </c>
       <c r="F154" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G154" t="s">
         <v>445</v>
@@ -9078,10 +9138,10 @@
         <v>37</v>
       </c>
       <c r="K154" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="L154" t="s">
-        <v>746</v>
+        <v>765</v>
       </c>
       <c r="M154" s="1">
         <v>58</v>
@@ -9107,7 +9167,7 @@
         <v>331</v>
       </c>
       <c r="F155" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G155" t="s">
         <v>445</v>
@@ -9122,10 +9182,10 @@
         <v>37</v>
       </c>
       <c r="K155" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="L155" t="s">
-        <v>747</v>
+        <v>766</v>
       </c>
       <c r="M155" s="1">
         <v>37</v>
@@ -9151,7 +9211,7 @@
         <v>332</v>
       </c>
       <c r="F156" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G156" t="s">
         <v>445</v>
@@ -9166,10 +9226,10 @@
         <v>37</v>
       </c>
       <c r="K156" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L156" t="s">
-        <v>748</v>
+        <v>767</v>
       </c>
       <c r="M156" s="1">
         <v>77</v>
@@ -9195,7 +9255,7 @@
         <v>333</v>
       </c>
       <c r="F157" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G157" t="s">
         <v>445</v>
@@ -9210,10 +9270,10 @@
         <v>37</v>
       </c>
       <c r="K157" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L157" t="s">
-        <v>748</v>
+        <v>768</v>
       </c>
       <c r="M157" s="1">
         <v>33</v>
